--- a/stories/arbres/ATOM-LAN.SON.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'assoit près de la fenêtre avec maman. Un son arrive : plic ploc. Maman dit : c'est un son. Quel nom ? Hugo dit : la pluie. Un autre son : tchou tchou. Hugo dit le nom : le train. Près du canapé, un miaulement. Hugo dit : le chat. Maman dit : on entend un son. On dit le nom. Hugo répète : son, nom. Plus tard, au jardin, la pluie a cessé. Un oiseau siffle. Hugo dit le nom : l'oiseau. Maman dit : tu as repris le geste. Même leçon, autre lieu. On nomme le son. La pluie, le train, le chat, l'oiseau.</t>
+          <t>Hugo s'assoit près de la fenêtre avec maman. Un son arrive : plic ploc. C'est un son. Quel nom ? La pluie. Un autre son : tchou tchou. Hugo dit le nom : le train. Près du canapé, un miaulement. Le chat. On entend un son. On dit le nom. Hugo répète : son, nom. Plus tard, au jardin, la pluie a cessé. Un oiseau siffle. Hugo dit le nom : l'oiseau. Tu as repris le geste. Même leçon, autre lieu. On nomme le son. La pluie, le train, le chat, l'oiseau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'assoit près de la fenêtre avec maman. Un son arrive : plic ploc.
+maman|C'est un son. Quel nom ?
+enfant-m|La pluie.
+narrateur|Un autre son : tchou tchou. Hugo dit le nom : le train. Près du canapé, un miaulement.
+enfant-m|Le chat.
+maman|On entend un son. On dit le nom.
+narrateur|Hugo répète : son, nom. Plus tard, au jardin, la pluie a cessé. Un oiseau siffle. Hugo dit le nom : l'oiseau.
+maman|Tu as repris le geste. Même leçon, autre lieu. On nomme le son.
+narrateur|La pluie, le train, le chat, l'oiseau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo entend un bruit. C'est quoi ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman donne la main. Hugo écoute encore le jardin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|La pluie, le train, le chat, l'oiseau.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Hugo entend un bruit. C'est quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Hugo a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Maman donne la main. Hugo écoute encore le jardin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-LAN.SON.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hugo nomme les sons de la fenêtre</t>
+          <t>La fenêtre de Raphaël</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le rideau bouge. Raphaël nomme la pluie, le train, le chat. Au jardin, il nomme l'oiseau.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'assoit près de la fenêtre avec maman. Un son arrive : plic ploc. C'est un son. Quel nom ? La pluie. Un autre son : tchou tchou. Hugo dit le nom : le train. Près du canapé, un miaulement. Le chat. On entend un son. On dit le nom. Hugo répète : son, nom. Plus tard, au jardin, la pluie a cessé. Un oiseau siffle. Hugo dit le nom : l'oiseau. Tu as repris le geste. Même leçon, autre lieu. On nomme le son. La pluie, le train, le chat, l'oiseau.</t>
+          <t>Le rideau du salon se lève un peu. Une goutte glisse sur la vitre. Le bol du chat cliquette, vide. Un coussin a un carré de soleil. Au loin, on entend le marché. Ça sent le savon du linge. Raphaël, viens près de la fenêtre. En ce moment, Raphaël s'assoit sur le rebord. Le bois du rebord est lisse et froid. Un son arrive. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Les gouttes font des chemins sur le verre. Elles descendent, maman. Oui. Plus loin, un son long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Près du canapé, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Son. Nom. Le chat vient frotter le mollet. Son poil est chaud. Plus tard, au jardin, la pluie a cessé. L'herbe sent le mouillé. Un oiseau siffle dans le cerisier. Cui cui. L'oiseau. Oui. Au jardin aussi, on nomme le son. Tu as dit le nom. La pluie, le train, le chat, l'oiseau. Bravo, Raphaël. Tu as dit le nom. Tu as fait du bon travail. J'écoute encore. D'accord. Le cerisier sent le fruit mouillé. Une goutte tombe d'une feuille. Plic. Oui. C'est un son. Quel nom ? La pluie. Oui. Le chat s'assoit dans l'herbe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'assoit près de la fenêtre avec maman. Un son arrive : plic ploc.
-maman|C'est un son. Quel nom ?
+          <t>narrateur|Le rideau du salon se lève un peu.
+narrateur|Une goutte glisse sur la vitre.
+narrateur|Le bol du chat cliquette, vide.
+narrateur|Un coussin a un carré de soleil.
+narrateur|Au loin, on entend le marché.
+narrateur|Ça sent le savon du linge.
+maman|Raphaël, viens près de la fenêtre.
+narrateur|En ce moment, Raphaël s'assoit sur le rebord.
+narrateur|Le bois du rebord est lisse et froid.
+narrateur|Un son arrive.
+narrateur|Plic ploc.
+maman|C'est un son.
+maman|Quel nom ?
 enfant-m|La pluie.
-narrateur|Un autre son : tchou tchou. Hugo dit le nom : le train. Près du canapé, un miaulement.
+maman|Oui.
+maman|Le nom du son, c'est la pluie.
+narrateur|Les gouttes font des chemins sur le verre.
+enfant-m|Elles descendent, maman.
+maman|Oui.
+narrateur|Plus loin, un son long.
+narrateur|Tchou tchou.
+maman|Encore un son.
+maman|Quel nom ?
+enfant-m|Le train.
+maman|Oui.
+maman|Le nom du son, c'est le train.
+narrateur|Près du canapé, un miaulement.
+narrateur|Miaou.
+maman|Un son.
+maman|Quel nom ?
 enfant-m|Le chat.
-maman|On entend un son. On dit le nom.
-narrateur|Hugo répète : son, nom. Plus tard, au jardin, la pluie a cessé. Un oiseau siffle. Hugo dit le nom : l'oiseau.
-maman|Tu as repris le geste. Même leçon, autre lieu. On nomme le son.
-narrateur|La pluie, le train, le chat, l'oiseau.</t>
+maman|Oui.
+maman|On entend un son.
+maman|On dit le nom.
+enfant-m|Son.
+enfant-m|Nom.
+narrateur|Le chat vient frotter le mollet.
+narrateur|Son poil est chaud.
+narrateur|Plus tard, au jardin, la pluie a cessé.
+narrateur|L'herbe sent le mouillé.
+narrateur|Un oiseau siffle dans le cerisier.
+narrateur|Cui cui.
+enfant-m|L'oiseau.
+maman|Oui.
+maman|Au jardin aussi, on nomme le son.
+maman|Tu as dit le nom.
+narrateur|La pluie, le train, le chat, l'oiseau.
+maman|Bravo, Raphaël.
+maman|Tu as dit le nom.
+maman|Tu as fait du bon travail.
+enfant-m|J'écoute encore.
+maman|D'accord.
+narrateur|Le cerisier sent le fruit mouillé.
+narrateur|Une goutte tombe d'une feuille.
+enfant-m|Plic.
+maman|Oui.
+maman|C'est un son.
+maman|Quel nom ?
+enfant-m|La pluie.
+maman|Oui.
+narrateur|Le chat s'assoit dans l'herbe.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1348,7 +1412,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo entend un bruit. C'est quoi ?</t>
+          <t>Raphaël entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1568,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo entend un bruit. C'est quoi ?</t>
+          <t>narrateur|Raphaël entend un bruit.
+narrateur|C'est quoi ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
+          <t>Raphaël a entendu un son. Il a dit le nom. Pluie. Train. Chat. Oiseau. Tu as nommé le son, à la fenêtre et au jardin ? Oui, maman. Bravo. Tu as fait du bon travail. Une feuille goutte encore. Raphaël tend l'oreille vers le cerisier. L'oiseau est là. Oui. On entend un son. On dit le nom. Le chat suit, tout bas. L'herbe mouille les chaussettes. Elles sont froides. Oui. On a entendu des sons. On a dit les noms. Pluie, train, chat, oiseau. Bravo. Le coussin du salon attend encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1741,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a entendu un son. Il a dit le nom. Pluie. Train. Chat.</t>
+          <t>narrateur|Raphaël a entendu un son.
+narrateur|Il a dit le nom.
+narrateur|Pluie.
+narrateur|Train.
+narrateur|Chat.
+narrateur|Oiseau.
+maman|Tu as nommé le son, à la fenêtre et au jardin ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Une feuille goutte encore.
+narrateur|Raphaël tend l'oreille vers le cerisier.
+enfant-m|L'oiseau est là.
+maman|Oui.
+maman|On entend un son.
+maman|On dit le nom.
+narrateur|Le chat suit, tout bas.
+narrateur|L'herbe mouille les chaussettes.
+enfant-m|Elles sont froides.
+maman|Oui.
+maman|On a entendu des sons.
+maman|On a dit les noms.
+enfant-m|Pluie, train, chat, oiseau.
+maman|Bravo.
+narrateur|Le coussin du salon attend encore.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman donne la main. Hugo écoute encore le jardin.</t>
+          <t>Tu me donnes la main ? Oui. Maman donne la main. Raphaël écoute encore le jardin. Une goutte tombe d'une feuille. Tu as fini d'écouter ? Oui, maman. Merci. Bravo. Le cerisier sent le fruit mouillé. Le chat rentre le premier. Tu as nommé le son, Raphaël. Oui. Les chaussettes laissent des traces. Le jardin sent encore la pluie.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1933,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman donne la main. Hugo écoute encore le jardin.</t>
+          <t>maman|Tu me donnes la main ?
+enfant-m|Oui.
+narrateur|Maman donne la main.
+narrateur|Raphaël écoute encore le jardin.
+narrateur|Une goutte tombe d'une feuille.
+maman|Tu as fini d'écouter ?
+enfant-m|Oui, maman.
+maman|Merci.
+maman|Bravo.
+narrateur|Le cerisier sent le fruit mouillé.
+narrateur|Le chat rentre le premier.
+maman|Tu as nommé le son, Raphaël.
+enfant-m|Oui.
+narrateur|Les chaussettes laissent des traces.
+narrateur|Le jardin sent encore la pluie.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1975,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Pluie, train, chat, oiseau. Bravo, Raphaël. La vitre du salon redevient calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2115,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit le nom.
+maman|Oui.
+maman|Pluie, train, chat, oiseau.
+maman|Bravo, Raphaël.
+narrateur|La vitre du salon redevient calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2180,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-08.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le rideau du salon se lève un peu. Une goutte glisse sur la vitre. Le bol du chat cliquette, vide. Un coussin a un carré de soleil. Au loin, on entend le marché. Ça sent le savon du linge. Raphaël, viens près de la fenêtre. En ce moment, Raphaël s'assoit sur le rebord. Le bois du rebord est lisse et froid. Un son arrive. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Les gouttes font des chemins sur le verre. Elles descendent, maman. Oui. Plus loin, un son long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Près du canapé, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Son. Nom. Le chat vient frotter le mollet. Son poil est chaud. Plus tard, au jardin, la pluie a cessé. L'herbe sent le mouillé. Un oiseau siffle dans le cerisier. Cui cui. L'oiseau. Oui. Au jardin aussi, on nomme le son. Tu as dit le nom. La pluie, le train, le chat, l'oiseau. Bravo, Raphaël. Tu as dit le nom. Tu as fait du bon travail. J'écoute encore. D'accord. Le cerisier sent le fruit mouillé. Une goutte tombe d'une feuille. Plic. Oui. C'est un son. Quel nom ? La pluie. Oui. Le chat s'assoit dans l'herbe.</t>
+          <t>Le rideau du salon se lève un peu. Une goutte glisse sur la vitre. Le bol du chat cliquette, vide. Un coussin a un carré de soleil. Au loin, on entend le marché. Ça sent le savon du linge. Raphaël, viens près de la fenêtre. En ce moment, Raphaël s'assoit sur le rebord. Le bois du rebord est lisse et froid. Un son arrive. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Les gouttes font des chemins sur le verre. Elles descendent, maman. Oui. Plus loin, un son long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Près du canapé, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Son. Nom. Le chat vient frotter le mollet. Son poil est chaud. Plus tard, au jardin, la pluie a cessé. L'herbe sent le mouillé. Un oiseau siffle dans le cerisier. Cui cui. L'oiseau. Oui. Au jardin aussi, on nomme le son. Tu as dit le nom. La pluie, le train, le chat, l'oiseau. Bravo, Raphaël. Tu as dit le nom. J'écoute encore. D'accord. Le cerisier sent le fruit mouillé. Une goutte tombe d'une feuille. Plic. Oui. C'est un son. Quel nom ? La pluie. Oui. Le chat s'assoit dans l'herbe.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo s'assoit près de la fenêtre avec maman. Un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt; arrive : plic ploc. Maman dit : c'est un son. Quel nom ? Hugo dit : la pluie. Un autre son : tchou tchou. Hugo dit le nom : le train. Près du canapé, un miaulement. Hugo dit : le chat. Maman dit : on entend un son. On dit le nom. Hugo répète : son, nom. Plus tard, au jardin, la pluie a cessé. Un oiseau siffle. Hugo dit le nom : l'oiseau. Maman dit : tu as repris le geste. Même leçon, autre lieu. On nomme le son. La pluie, le train, le chat, l'oiseau.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le rideau du salon se lève un peu. Une goutte glisse sur la vitre. Le bol du chat cliquette, vide. Un coussin a un carré de soleil. Au loin, on entend le marché. Ça sent le savon du linge. Raphaël, viens près de la fenêtre. En ce moment, Raphaël s'assoit sur le rebord. Le bois du rebord est lisse et froid. Un son arrive. Plic ploc. C'est un son. Quel nom ? La pluie. Oui. Le nom du son, c'est la pluie. Les gouttes font des chemins sur le verre. Elles descendent, maman. Oui. Plus loin, un son long. Tchou tchou. Encore un son. Quel nom ? Le train. Oui. Le nom du son, c'est le train. Près du canapé, un miaulement. Miaou. Un son. Quel nom ? Le chat. Oui. On entend un son. On dit le nom. Son. Nom. Le chat vient frotter le mollet. Son poil est chaud. Plus tard, au jardin, la pluie a cessé. L'herbe sent le mouillé. Un oiseau siffle dans le cerisier. Cui cui. L'oiseau. Oui. Au jardin aussi, on nomme le son. Tu as dit le nom. La pluie, le train, le chat, l'oiseau. Bravo, Raphaël. Tu as dit le nom. J'écoute encore. D'accord. Le cerisier sent le fruit mouillé. Une goutte tombe d'une feuille. Plic. Oui. C'est un son. Quel nom ? La pluie. Oui. Le chat s'assoit dans l'herbe.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1373,7 +1373,6 @@
 narrateur|La pluie, le train, le chat, l'oiseau.
 maman|Bravo, Raphaël.
 maman|Tu as dit le nom.
-maman|Tu as fait du bon travail.
 enfant-m|J'écoute encore.
 maman|D'accord.
 narrateur|Le cerisier sent le fruit mouillé.
@@ -1387,7 +1386,6 @@
 narrateur|Le chat s'assoit dans l'herbe.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1417,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo entend un bruit. C'est quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël entend un bruit. C'est quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1572,7 +1570,6 @@
 narrateur|C'est quoi ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a entendu un son. Il a dit le nom. Pluie. Train. Chat. Oiseau. Tu as nommé le son, à la fenêtre et au jardin ? Oui, maman. Bravo. Tu as fait du bon travail. Une feuille goutte encore. Raphaël tend l'oreille vers le cerisier. L'oiseau est là. Oui. On entend un son. On dit le nom. Le chat suit, tout bas. L'herbe mouille les chaussettes. Elles sont froides. Oui. On a entendu des sons. On a dit les noms. Pluie, train, chat, oiseau. Bravo. Le coussin du salon attend encore.</t>
+          <t>Raphaël a entendu un son. Il a dit le nom. Pluie. Train. Chat. Oiseau. Tu as nommé le son, à la fenêtre et au jardin ? Oui, maman. Bravo. Une feuille goutte encore. Raphaël tend l'oreille vers le cerisier. L'oiseau est là. Oui. On entend un son. On dit le nom. Le chat suit, tout bas. L'herbe mouille les chaussettes. Elles sont froides. Oui. On a entendu des sons. On a dit les noms. Pluie, train, chat, oiseau. Bravo. Le coussin du salon attend encore.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo a entendu un &lt;emphasis level="moderate"&gt;son&lt;/emphasis&gt;. Il a dit le nom. Pluie. Train. Chat.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a entendu un son. Il a dit le nom. Pluie. Train. Chat. Oiseau. Tu as nommé le son, à la fenêtre et au jardin ? Oui, maman. Bravo. Une feuille goutte encore. Raphaël tend l'oreille vers le cerisier. L'oiseau est là. Oui. On entend un son. On dit le nom. Le chat suit, tout bas. L'herbe mouille les chaussettes. Elles sont froides. Oui. On a entendu des sons. On a dit les noms. Pluie, train, chat, oiseau. Bravo. Le coussin du salon attend encore.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1747,6 @@
 maman|Tu as nommé le son, à la fenêtre et au jardin ?
 enfant-m|Oui, maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 narrateur|Une feuille goutte encore.
 narrateur|Raphaël tend l'oreille vers le cerisier.
 enfant-m|L'oiseau est là.
@@ -1768,7 +1764,6 @@
 narrateur|Le coussin du salon attend encore.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1798,7 +1793,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;. Hugo écoute encore le jardin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Tu me donnes la main ? Oui. Maman donne la main. Raphaël écoute encore le jardin. Une goutte tombe d'une feuille. Tu as fini d'écouter ? Oui, maman. Merci. Bravo. Le cerisier sent le fruit mouillé. Le chat rentre le premier. Tu as nommé le son, Raphaël. Oui. Les chaussettes laissent des traces. Le jardin sent encore la pluie.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1950,7 +1945,6 @@
 narrateur|Le jardin sent encore la pluie.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1975,12 +1969,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le nom. Oui. Pluie, train, chat, oiseau. Bravo, Raphaël. La vitre du salon redevient calme. L'histoire est finie.</t>
+          <t>J'ai dit le nom. Oui. Pluie, train, chat, oiseau. Bravo, Raphaël. La vitre du salon redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le nom. Oui. Pluie, train, chat, oiseau. Bravo, Raphaël. La vitre du salon redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2119,11 +2113,9 @@
 maman|Oui.
 maman|Pluie, train, chat, oiseau.
 maman|Bravo, Raphaël.
-narrateur|La vitre du salon redevient calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La vitre du salon redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2142,7 +2134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2187,6 +2179,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-LAN.SON.001-08.xlsx
+++ b/stories/arbres/ATOM-LAN.SON.001-08.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, maman</t>
+          <t>Raphaël, maman</t>
         </is>
       </c>
     </row>
